--- a/reports/2026-09_月次実績報告/excel/第51期下期境港営業所担当者別実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期下期境港営業所担当者別実績.xlsx
@@ -27361,7 +27361,7 @@
         <v>6431.527</v>
       </c>
       <c r="F91" s="41" t="n">
-        <v>11141</v>
+        <v>11141.136</v>
       </c>
       <c r="G91" s="41" t="n">
         <v>28205.688</v>
@@ -27383,7 +27383,7 @@
         <v>1088.606</v>
       </c>
       <c r="M91" s="41" t="n">
-        <v>2462</v>
+        <v>2462.073</v>
       </c>
       <c r="N91" s="41" t="n">
         <v>6703.305</v>
@@ -27392,7 +27392,7 @@
         <v>1815.052</v>
       </c>
       <c r="P91" s="80" t="n">
-        <v>1564.721</v>
+        <v>1564.321</v>
       </c>
       <c r="Q91" s="41" t="n">
         <v>2864.973</v>
